--- a/p6_deployment/data/germany/data_understanding/df_match_player_next.xlsx
+++ b/p6_deployment/data/germany/data_understanding/df_match_player_next.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,199 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A2:A28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>pWQQJq6l</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>hIsO3XFj</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>EF8gXauC</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>lONsG15D</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>0K2qBFNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Kj4sifWp</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>bF2q76Mr</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>vyk5gjdE</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>tbKZHNz1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>MZjh9ghT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>f1nnRRDE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>8QPARz8c</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>hzyf0b9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>CpiTEcOi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>8CpxDyg4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6q2yrHgU</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>AiJ3kset</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>YV3TqwPH</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>l0ueP5rR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>t2AoZLAa</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>jFMCm08e</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>tvOIPExA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>KSwfVwAO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>pzHxyrtm</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>dCPKovw8</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>vXAKoaf5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>fcxqFy2l</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/p6_deployment/data/germany/data_understanding/df_match_player_next.xlsx
+++ b/p6_deployment/data/germany/data_understanding/df_match_player_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A28"/>
+  <dimension ref="A2:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -613,6 +613,34 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
+          <t>06NAdG8N</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Sff03OL7</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>EkP2bxvB</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>pAXo2Kvn</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
           <t>fcxqFy2l</t>
         </is>
       </c>
